--- a/artfynd/A 34513-2026 artfynd.xlsx
+++ b/artfynd/A 34513-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,27 +680,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136640563</v>
+        <v>136708611</v>
       </c>
       <c r="B2" t="n">
-        <v>58006</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,11 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503610</v>
+        <v>503611</v>
       </c>
       <c r="R2" t="n">
-        <v>6708839</v>
+        <v>6708727</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +753,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>födosökshack på död gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,24 +778,1074 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Eriksson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136708611</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136708624</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Trolldalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>503575</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6708801</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>födosökshack på död gran</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136708624</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136640563</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trolldalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>503610</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6708839</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136640563</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136708372</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Trolldalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>503374</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6709027</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136708372</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136708385</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trolldalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>503469</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6708987</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack på tall, nyligen omkull blåst.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136708385</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136708398</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Trolldalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>503477</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6708976</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136708398</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136708529</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Trolldalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>503584</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6708985</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136708529</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136708566</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Trolldalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>503705</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6708610</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136708566</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136708578</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Trolldalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>503667</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6708702</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136708578</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136708596</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Trolldalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>503594</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6708733</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136708596</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34513-2026 artfynd.xlsx
+++ b/artfynd/A 34513-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708611</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136708624</v>
       </c>
       <c r="B3" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136640563</v>
       </c>
       <c r="B4" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136708372</v>
       </c>
       <c r="B5" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136708385</v>
       </c>
       <c r="B6" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>136708398</v>
       </c>
       <c r="B7" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136708529</v>
       </c>
       <c r="B8" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136708566</v>
       </c>
       <c r="B9" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136708578</v>
       </c>
       <c r="B10" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>136708596</v>
       </c>
       <c r="B11" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34513-2026 artfynd.xlsx
+++ b/artfynd/A 34513-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708611</v>
       </c>
       <c r="B2" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136708624</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136640563</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136708372</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136708385</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>136708398</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136708529</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136708566</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136708578</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>136708596</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34513-2026 artfynd.xlsx
+++ b/artfynd/A 34513-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708611</v>
       </c>
       <c r="B2" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136708624</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136640563</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136708372</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136708385</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>136708398</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136708529</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136708566</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136708578</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>136708596</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34513-2026 artfynd.xlsx
+++ b/artfynd/A 34513-2026 artfynd.xlsx
@@ -711,11 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -826,11 +822,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -1062,11 +1054,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1177,11 +1165,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1292,11 +1276,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1407,11 +1387,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1522,11 +1498,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1637,11 +1609,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1752,11 +1720,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>

--- a/artfynd/A 34513-2026 artfynd.xlsx
+++ b/artfynd/A 34513-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136708611</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136708624</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136708372</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136708385</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136708398</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136708529</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136708566</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>136708578</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136708596</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
